--- a/docs/Final Req Docs/Book1.xlsx
+++ b/docs/Final Req Docs/Book1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pointsolve-my.sharepoint.com/personal/swest_anukiconsulting_com/Documents/LocalWest/Projects/GCC Database Solution/GCCWebApp/GCCWebApp/docs/Final Req Docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9D64F60C-56F0-4482-9AB5-E4F01076CFF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{9D64F60C-56F0-4482-9AB5-E4F01076CFF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10F1C9E8-16CB-459B-9A42-404952D3FD0F}"/>
   <bookViews>
-    <workbookView xWindow="28770" yWindow="-16305" windowWidth="29040" windowHeight="15720" xr2:uid="{17585D4D-B952-4E95-836F-D9C185FC05EC}"/>
+    <workbookView xWindow="-30" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{17585D4D-B952-4E95-836F-D9C185FC05EC}"/>
   </bookViews>
   <sheets>
     <sheet name="Final Design Cleanup Tracker" sheetId="1" r:id="rId1"/>
@@ -164,7 +164,6 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C494E60F-32FE-4CC2-8322-3307E3CE094E}" name="Table1" displayName="Table1" ref="A1:F33" totalsRowShown="0">
-  <autoFilter ref="A1:F33" xr:uid="{C494E60F-32FE-4CC2-8322-3307E3CE094E}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{3EB6F73E-D70B-418C-824E-84B3FEF9B1EE}" name="ID"/>
     <tableColumn id="2" xr3:uid="{7454FE02-3907-4D7D-A818-4C086414440D}" name="Page/Context"/>
@@ -521,7 +520,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -535,7 +534,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -563,7 +562,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -591,7 +590,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="105" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -605,7 +604,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
